--- a/data/trans_dic/P11_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 25,2</t>
+          <t>19,27; 25,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,02; 22,2</t>
+          <t>16,07; 22,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,65; 23,5</t>
+          <t>17,36; 23,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,23; 34,45</t>
+          <t>27,2; 34,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,95; 32,89</t>
+          <t>26,73; 33,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,33; 37,91</t>
+          <t>30,21; 38,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,45; 36,32</t>
+          <t>28,63; 36,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,37; 43,08</t>
+          <t>37,26; 43,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,8; 28,34</t>
+          <t>23,72; 28,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23,89; 29,2</t>
+          <t>24,19; 28,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,27; 29,05</t>
+          <t>24,17; 29,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,2; 38,06</t>
+          <t>33,2; 37,95</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 18,01</t>
+          <t>13,45; 18,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,15; 23,54</t>
+          <t>18,04; 23,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,1; 21,18</t>
+          <t>16,55; 21,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 25,08</t>
+          <t>9,34; 25,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,97; 29,84</t>
+          <t>23,91; 29,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,62; 34,58</t>
+          <t>28,51; 34,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,3; 33,34</t>
+          <t>27,41; 33,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,13; 40,39</t>
+          <t>35,44; 40,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,31; 23,15</t>
+          <t>19,29; 22,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,06; 28,11</t>
+          <t>24,32; 28,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,46; 26,52</t>
+          <t>22,45; 26,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,8; 31,99</t>
+          <t>17,74; 31,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,34; 22,7</t>
+          <t>16,37; 22,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,89; 16,06</t>
+          <t>10,99; 16,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,69; 20,22</t>
+          <t>14,7; 20,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,82; 27,38</t>
+          <t>20,49; 27,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,64; 39,22</t>
+          <t>31,52; 38,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,05; 32,15</t>
+          <t>25,1; 31,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,6; 30,15</t>
+          <t>23,49; 30,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,99; 70,5</t>
+          <t>28,67; 76,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,9; 29,69</t>
+          <t>24,79; 29,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,75; 23,16</t>
+          <t>18,82; 23,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,94; 24,34</t>
+          <t>19,86; 24,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,22; 57,49</t>
+          <t>26,29; 56,28</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 19,71</t>
+          <t>14,86; 19,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,3; 23,97</t>
+          <t>18,6; 24,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,57; 20,69</t>
+          <t>15,63; 20,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 31,76</t>
+          <t>25,85; 31,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,63; 30,0</t>
+          <t>24,55; 30,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,51; 34,62</t>
+          <t>29,01; 34,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 29,88</t>
+          <t>23,92; 29,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,32; 41,45</t>
+          <t>30,24; 41,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,42; 24,28</t>
+          <t>20,69; 24,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,69; 28,77</t>
+          <t>24,77; 28,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,73; 24,49</t>
+          <t>20,6; 24,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 35,96</t>
+          <t>29,71; 35,58</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,88; 19,62</t>
+          <t>16,92; 19,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,5; 20,28</t>
+          <t>17,54; 20,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,35; 19,91</t>
+          <t>17,31; 20,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,57; 27,47</t>
+          <t>19,41; 27,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,56; 30,67</t>
+          <t>27,64; 30,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,71; 33,12</t>
+          <t>29,8; 33,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,35; 30,48</t>
+          <t>27,23; 30,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,8; 50,77</t>
+          <t>35,95; 51,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,75; 24,87</t>
+          <t>22,7; 24,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,18; 26,34</t>
+          <t>24,14; 26,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,75; 24,91</t>
+          <t>22,87; 24,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,64; 40,15</t>
+          <t>29,65; 38,99</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas</t>
+          <t>Población a la que el dolor le dificultó su trabajo habitual las últimas 4 semanas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>132259; 174879</t>
+          <t>133761; 175728</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>111763; 154888</t>
+          <t>112136; 154348</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>118096; 157252</t>
+          <t>116144; 158020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>172814; 218650</t>
+          <t>172632; 218779</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>178648; 226416</t>
+          <t>183979; 230559</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>210833; 263570</t>
+          <t>210018; 265428</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>189484; 241914</t>
+          <t>190700; 241294</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>252553; 291085</t>
+          <t>251758; 292531</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>328974; 391794</t>
+          <t>327909; 389946</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>332716; 406746</t>
+          <t>336984; 403605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>324085; 387913</t>
+          <t>322654; 389120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>435068; 498744</t>
+          <t>435111; 497333</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>128280; 173229</t>
+          <t>129338; 174227</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>183928; 238594</t>
+          <t>182833; 236595</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>163537; 215222</t>
+          <t>168183; 215856</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125319; 298589</t>
+          <t>111206; 301407</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>232085; 288955</t>
+          <t>231559; 289166</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>294854; 356242</t>
+          <t>293664; 355200</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>283918; 346725</t>
+          <t>285019; 347313</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>336033; 386402</t>
+          <t>339013; 389383</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>372743; 446820</t>
+          <t>372426; 442801</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>491769; 574558</t>
+          <t>496973; 576251</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>461731; 545148</t>
+          <t>461602; 543911</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>403580; 686973</t>
+          <t>380962; 679389</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>110889; 154007</t>
+          <t>111039; 155780</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82139; 121148</t>
+          <t>82894; 122682</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110581; 152188</t>
+          <t>110637; 155654</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146740; 192914</t>
+          <t>144368; 191485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>216379; 268190</t>
+          <t>215567; 266031</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>194645; 249864</t>
+          <t>195050; 246672</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>183748; 234695</t>
+          <t>182902; 234313</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>270390; 657662</t>
+          <t>267395; 711594</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>339177; 404517</t>
+          <t>337671; 403928</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>287161; 354775</t>
+          <t>288273; 355284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>305366; 372734</t>
+          <t>304121; 373156</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>429353; 941312</t>
+          <t>430460; 921593</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>139988; 185669</t>
+          <t>139991; 183880</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>172717; 226273</t>
+          <t>175568; 226891</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>145050; 192844</t>
+          <t>145627; 194914</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>237825; 294390</t>
+          <t>239547; 296503</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>255851; 311568</t>
+          <t>255020; 315188</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>299885; 364207</t>
+          <t>305167; 364037</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>246331; 310076</t>
+          <t>248156; 307551</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>331455; 453129</t>
+          <t>330567; 453747</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>404545; 480945</t>
+          <t>409749; 483545</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>492796; 574241</t>
+          <t>494311; 577310</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>408323; 482284</t>
+          <t>405809; 485351</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>598701; 726311</t>
+          <t>600202; 718733</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>552983; 642865</t>
+          <t>554337; 643076</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>596618; 691523</t>
+          <t>597889; 692568</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>584514; 670850</t>
+          <t>583392; 675663</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>676549; 949686</t>
+          <t>670918; 946553</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>931344; 1036340</t>
+          <t>933971; 1042379</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1056150; 1177238</t>
+          <t>1059235; 1173836</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>963266; 1073617</t>
+          <t>959073; 1071321</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1309506; 1857299</t>
+          <t>1314973; 1891058</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1514374; 1655188</t>
+          <t>1510899; 1649700</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1684174; 1834398</t>
+          <t>1681452; 1828983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1567702; 1716472</t>
+          <t>1576319; 1720911</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2109118; 2856413</t>
+          <t>2109545; 2774079</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P11_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P11_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,27; 25,32</t>
+          <t>19,0; 24,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,07; 22,12</t>
+          <t>15,93; 21,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 23,62</t>
+          <t>17,4; 23,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,2; 34,47</t>
+          <t>27,31; 34,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,73; 33,49</t>
+          <t>26,54; 33,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,21; 38,18</t>
+          <t>30,26; 37,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,63; 36,23</t>
+          <t>28,98; 36,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,26; 43,29</t>
+          <t>36,36; 42,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23,72; 28,21</t>
+          <t>23,7; 28,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24,19; 28,97</t>
+          <t>24,04; 28,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,17; 29,15</t>
+          <t>24,06; 29,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,2; 37,95</t>
+          <t>33,0; 37,75</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,45; 18,11</t>
+          <t>13,31; 17,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,04; 23,34</t>
+          <t>17,98; 23,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,55; 21,25</t>
+          <t>16,27; 20,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 25,32</t>
+          <t>21,05; 26,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,91; 29,86</t>
+          <t>23,41; 29,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,51; 34,48</t>
+          <t>28,43; 34,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,41; 33,4</t>
+          <t>27,5; 33,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>35,44; 40,7</t>
+          <t>34,69; 39,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,29; 22,94</t>
+          <t>19,35; 23,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,32; 28,2</t>
+          <t>24,09; 28,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,45; 26,46</t>
+          <t>22,76; 26,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,74; 31,64</t>
+          <t>28,71; 32,63</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,37; 22,96</t>
+          <t>16,37; 22,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,99; 16,26</t>
+          <t>10,81; 16,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,7; 20,68</t>
+          <t>14,64; 20,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,49; 27,17</t>
+          <t>20,99; 27,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,52; 38,9</t>
+          <t>31,03; 38,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,1; 31,74</t>
+          <t>25,21; 31,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,49; 30,1</t>
+          <t>23,63; 30,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,67; 76,29</t>
+          <t>27,88; 33,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,79; 29,65</t>
+          <t>24,83; 29,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,82; 23,2</t>
+          <t>18,69; 23,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,86; 24,37</t>
+          <t>19,83; 24,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,29; 56,28</t>
+          <t>25,24; 29,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,86; 19,52</t>
+          <t>14,67; 19,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 24,04</t>
+          <t>18,88; 24,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 20,92</t>
+          <t>15,69; 20,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,85; 31,99</t>
+          <t>25,38; 31,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,55; 30,35</t>
+          <t>24,57; 30,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,01; 34,61</t>
+          <t>28,9; 34,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,92; 29,64</t>
+          <t>23,97; 29,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,24; 41,51</t>
+          <t>37,7; 42,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 24,41</t>
+          <t>20,55; 24,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,77; 28,93</t>
+          <t>24,8; 28,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,6; 24,64</t>
+          <t>20,62; 24,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,71; 35,58</t>
+          <t>32,45; 36,45</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,92; 19,63</t>
+          <t>16,88; 19,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,54; 20,31</t>
+          <t>17,52; 20,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,31; 20,05</t>
+          <t>17,39; 20,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,41; 27,38</t>
+          <t>24,8; 27,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,64; 30,85</t>
+          <t>27,78; 30,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,8; 33,02</t>
+          <t>29,68; 32,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,23; 30,42</t>
+          <t>27,19; 30,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>35,95; 51,69</t>
+          <t>35,69; 38,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,7; 24,79</t>
+          <t>22,66; 24,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,14; 26,26</t>
+          <t>24,22; 26,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,87; 24,97</t>
+          <t>22,78; 24,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,65; 38,99</t>
+          <t>30,92; 33,08</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>195904</t>
+          <t>211256</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>271221</t>
+          <t>288516</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>467125</t>
+          <t>499772</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>133761; 175728</t>
+          <t>131854; 173328</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>112136; 154348</t>
+          <t>111168; 152232</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>116144; 158020</t>
+          <t>116435; 158723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>172632; 218779</t>
+          <t>188390; 235350</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>183979; 230559</t>
+          <t>182662; 229769</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>210018; 265428</t>
+          <t>210371; 263394</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>190700; 241294</t>
+          <t>192999; 240923</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>251758; 292531</t>
+          <t>266579; 309084</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>327909; 389946</t>
+          <t>327567; 393313</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>336984; 403605</t>
+          <t>334841; 400648</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>322654; 389120</t>
+          <t>321272; 387277</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>435111; 497333</t>
+          <t>469506; 537168</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229403</t>
+          <t>250482</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>362999</t>
+          <t>398958</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>592402</t>
+          <t>649441</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>129338; 174227</t>
+          <t>127971; 172409</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>182833; 236595</t>
+          <t>182219; 237560</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168183; 215856</t>
+          <t>165290; 213194</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111206; 301407</t>
+          <t>220284; 278333</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>231559; 289166</t>
+          <t>226729; 284868</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>293664; 355200</t>
+          <t>292913; 355587</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>285019; 347313</t>
+          <t>285970; 347541</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>339013; 389383</t>
+          <t>370886; 425651</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>372426; 442801</t>
+          <t>373485; 445708</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>496973; 576251</t>
+          <t>492299; 577599</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>461602; 543911</t>
+          <t>467982; 547342</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>380962; 679389</t>
+          <t>607345; 690322</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>168779</t>
+          <t>192867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>422594</t>
+          <t>249082</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>591373</t>
+          <t>441949</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>111039; 155780</t>
+          <t>111070; 154479</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82894; 122682</t>
+          <t>81584; 121623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>110637; 155654</t>
+          <t>110235; 154325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144368; 191485</t>
+          <t>168589; 221537</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>215567; 266031</t>
+          <t>212208; 264614</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>195050; 246672</t>
+          <t>195944; 245932</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>182902; 234313</t>
+          <t>183921; 235133</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>267395; 711594</t>
+          <t>226235; 272649</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>337671; 403928</t>
+          <t>338273; 405337</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>288273; 355284</t>
+          <t>286323; 352432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>304121; 373156</t>
+          <t>303634; 369962</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>430460; 921593</t>
+          <t>407521; 476872</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>265719</t>
+          <t>278707</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>413918</t>
+          <t>448537</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>679637</t>
+          <t>727244</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>139991; 183880</t>
+          <t>138267; 183735</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>175568; 226891</t>
+          <t>178224; 231248</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>145627; 194914</t>
+          <t>146239; 194295</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>239547; 296503</t>
+          <t>251293; 308327</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>255020; 315188</t>
+          <t>255214; 311843</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>305167; 364037</t>
+          <t>303994; 365219</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>248156; 307551</t>
+          <t>248748; 306001</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>330567; 453747</t>
+          <t>421074; 479693</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>409749; 483545</t>
+          <t>406990; 479358</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>494311; 577310</t>
+          <t>494865; 572714</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>405809; 485351</t>
+          <t>406161; 485246</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>600202; 718733</t>
+          <t>683660; 767906</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>859805</t>
+          <t>933312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1470732</t>
+          <t>1385094</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2330537</t>
+          <t>2318406</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>554337; 643076</t>
+          <t>553244; 639974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>597889; 692568</t>
+          <t>597213; 692784</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>583392; 675663</t>
+          <t>585906; 673772</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>670918; 946553</t>
+          <t>875133; 985944</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>933971; 1042379</t>
+          <t>938814; 1044684</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1059235; 1173836</t>
+          <t>1054956; 1165572</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>959073; 1071321</t>
+          <t>957490; 1065099</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1314973; 1891058</t>
+          <t>1331342; 1435380</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1510899; 1649700</t>
+          <t>1508456; 1648796</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1681452; 1828983</t>
+          <t>1686514; 1834573</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1576319; 1720911</t>
+          <t>1570059; 1711007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2109545; 2774079</t>
+          <t>2244434; 2401930</t>
         </is>
       </c>
     </row>
